--- a/thesis/data/table_literature_review.xlsx
+++ b/thesis/data/table_literature_review.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mateo\Documents\Universidad\Master\Thesis\BEReBASL\thesis\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4D821991-0581-4860-A5EF-6C95E04EBE94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D48BC701-6987-4F95-920C-657844658540}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-3135" windowWidth="29040" windowHeight="15720" xr2:uid="{D47D74D5-B8DF-4140-AD42-DCD0A14E194D}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D47D74D5-B8DF-4140-AD42-DCD0A14E194D}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -39,18 +39,105 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
     <t>Reference</t>
   </si>
   <si>
-    <t>Formalization method</t>
-  </si>
-  <si>
-    <t>Theoretically founded</t>
-  </si>
-  <si>
-    <t>Considers dynamic perspective</t>
+    <t>Assumptions-Transparent</t>
+  </si>
+  <si>
+    <t>Dynamic perspective</t>
+  </si>
+  <si>
+    <t>Theoretical Discussion</t>
+  </si>
+  <si>
+    <t>What is needed for RI to work?</t>
+  </si>
+  <si>
+    <t>Distributional assumptions, sample of reject region or experts judgement</t>
+  </si>
+  <si>
+    <t>Concludes RI can (reliably) work?</t>
+  </si>
+  <si>
+    <t>Only with full sample of reject region</t>
+  </si>
+  <si>
+    <t>How to leverage rejects?</t>
+  </si>
+  <si>
+    <t>Estimation of $p(x)$ for further usage in EM based methods</t>
+  </si>
+  <si>
+    <t>Main challenge</t>
+  </si>
+  <si>
+    <t>Economic costs of sample</t>
+  </si>
+  <si>
+    <t>Anderson2019_BayesianNetForRI</t>
+  </si>
+  <si>
+    <t>HandHanley1993CanRIWork</t>
+  </si>
+  <si>
+    <t>Reliability of causality and dimensionality</t>
+  </si>
+  <si>
+    <t>Knowledge and existence of causal non-cyclic relationships between features</t>
+  </si>
+  <si>
+    <t>Extrapolation to rejects through bayesian network, then build scorecard on augemented sample</t>
+  </si>
+  <si>
+    <t>Moderately</t>
+  </si>
+  <si>
+    <t>Li_et_al_2017_semisupervised_svm</t>
+  </si>
+  <si>
+    <t>Rejects guide the decision boundary through low density regions in the features space</t>
+  </si>
+  <si>
+    <t>High dimensional feature space problematic</t>
+  </si>
+  <si>
+    <t>Yes, evaluation method is unreliable</t>
+  </si>
+  <si>
+    <t>Low density regions of features space aligned with known labels separation</t>
+  </si>
+  <si>
+    <t>Bucker_etal_2013_MNAR_RI</t>
+  </si>
+  <si>
+    <t>Label missingness be independent across observations</t>
+  </si>
+  <si>
+    <t>Independence condition is illogical in dynamic context, numerical problems</t>
+  </si>
+  <si>
+    <t>Estimation of unconditional means of features and probability of reject</t>
+  </si>
+  <si>
+    <t>Yes, in theoretical and simulation based results</t>
+  </si>
+  <si>
+    <t>Banasik01032010</t>
+  </si>
+  <si>
+    <t>No, maybe with high rejection rates</t>
+  </si>
+  <si>
+    <t>Augmentation via reweighting using accepts rejects model</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Augmentation is not adequate for RI</t>
   </si>
 </sst>
 </file>
@@ -94,9 +181,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -431,30 +521,180 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8852FF5C-5175-44DA-A620-18833DBB2C7A}">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.21875" customWidth="1"/>
-    <col min="4" max="4" width="27.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.21875" customWidth="1"/>
+    <col min="3" max="3" width="21.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.6640625" customWidth="1"/>
+    <col min="5" max="5" width="24.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="27.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="27.44140625" customWidth="1"/>
+    <col min="8" max="8" width="27.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" t="s">
         <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
       </c>
       <c r="D1" t="s">
         <v>3</v>
       </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D3" s="1"/>
+    <row r="2" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="b">
+        <v>1</v>
+      </c>
+      <c r="D2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" t="b">
+        <v>1</v>
+      </c>
+      <c r="D5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" t="b">
+        <v>1</v>
+      </c>
+      <c r="D6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" s="1"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D11" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/thesis/data/table_literature_review.xlsx
+++ b/thesis/data/table_literature_review.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mateo\Documents\Universidad\Master\Thesis\BEReBASL\thesis\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D48BC701-6987-4F95-920C-657844658540}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C71D36AC-C6C5-49E8-BDF6-2268837DBE54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D47D74D5-B8DF-4140-AD42-DCD0A14E194D}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="Hoja2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,23 +40,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="41">
   <si>
     <t>Reference</t>
   </si>
   <si>
-    <t>Assumptions-Transparent</t>
-  </si>
-  <si>
     <t>Dynamic perspective</t>
   </si>
   <si>
-    <t>Theoretical Discussion</t>
-  </si>
-  <si>
-    <t>What is needed for RI to work?</t>
-  </si>
-  <si>
     <t>Distributional assumptions, sample of reject region or experts judgement</t>
   </si>
   <si>
@@ -65,9 +57,6 @@
     <t>Only with full sample of reject region</t>
   </si>
   <si>
-    <t>How to leverage rejects?</t>
-  </si>
-  <si>
     <t>Estimation of $p(x)$ for further usage in EM based methods</t>
   </si>
   <si>
@@ -134,10 +123,46 @@
     <t>Augmentation via reweighting using accepts rejects model</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
     <t>Augmentation is not adequate for RI</t>
+  </si>
+  <si>
+    <t>RI approach</t>
+  </si>
+  <si>
+    <t>RI Approach</t>
+  </si>
+  <si>
+    <t>Key identifying assumptions</t>
+  </si>
+  <si>
+    <t>Accept reject model estimable</t>
+  </si>
+  <si>
+    <t>Assumptions explicit?</t>
+  </si>
+  <si>
+    <t>Theoretical/heuristic justification?</t>
+  </si>
+  <si>
+    <t>Infers Rejects label for evaluation?</t>
+  </si>
+  <si>
+    <t>Type of result</t>
+  </si>
+  <si>
+    <t>Theoretical</t>
+  </si>
+  <si>
+    <t>Empirical</t>
+  </si>
+  <si>
+    <t>Theoretical and simulation</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>No</t>
   </si>
 </sst>
 </file>
@@ -521,180 +546,263 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8852FF5C-5175-44DA-A620-18833DBB2C7A}">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="28.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.21875" customWidth="1"/>
-    <col min="3" max="3" width="21.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.6640625" customWidth="1"/>
-    <col min="5" max="5" width="24.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="27.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="27.44140625" customWidth="1"/>
-    <col min="8" max="8" width="27.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="28.21875" customWidth="1"/>
+    <col min="4" max="4" width="21.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.6640625" customWidth="1"/>
+    <col min="6" max="6" width="28.6640625" customWidth="1"/>
+    <col min="7" max="7" width="24.88671875" customWidth="1"/>
+    <col min="8" max="8" width="27.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="27.44140625" customWidth="1"/>
+    <col min="10" max="10" width="27.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="C1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H1" t="s">
+    </row>
+    <row r="2" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" t="b">
-        <v>1</v>
       </c>
       <c r="D2" t="b">
         <v>1</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" s="2" t="s">
+      <c r="E2" t="b">
+        <v>1</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="J2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="H2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="2" t="s">
+      <c r="D3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F3" t="s">
+        <v>40</v>
+      </c>
+      <c r="G3" t="s">
+        <v>37</v>
+      </c>
+      <c r="H3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="J3" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F4" t="s">
+        <v>39</v>
+      </c>
+      <c r="G4" t="s">
+        <v>37</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C3" t="b">
-        <v>1</v>
-      </c>
-      <c r="D3" t="b">
-        <v>0</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H3" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" s="2" t="s">
+      <c r="J4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>19</v>
       </c>
-      <c r="C4" t="b">
-        <v>0</v>
-      </c>
-      <c r="D4" t="b">
-        <v>0</v>
-      </c>
-      <c r="E4" s="2" t="s">
+      <c r="B5" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G4" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="H4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5" t="b">
-        <v>1</v>
       </c>
       <c r="D5" t="b">
         <v>1</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F5" t="s">
+        <v>40</v>
+      </c>
+      <c r="G5" t="s">
+        <v>38</v>
+      </c>
+      <c r="H5" t="s">
+        <v>23</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
         <v>24</v>
       </c>
-      <c r="F5" t="s">
-        <v>27</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>28</v>
-      </c>
       <c r="B6" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C6" t="b">
-        <v>1</v>
+        <v>26</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="D6" t="b">
         <v>1</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="E6" t="b">
+        <v>1</v>
+      </c>
+      <c r="F6" t="s">
+        <v>40</v>
+      </c>
+      <c r="G6" t="s">
+        <v>37</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="D11" s="1"/>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E11" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD0A6221-C3E5-43E7-83EA-25D1D90EAB9E}">
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="29.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>24</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/thesis/data/table_literature_review.xlsx
+++ b/thesis/data/table_literature_review.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mateo\Documents\Universidad\Master\Thesis\BEReBASL\thesis\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C71D36AC-C6C5-49E8-BDF6-2268837DBE54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82B1D8F4-4D95-4C80-9875-71E7B245E65D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D47D74D5-B8DF-4140-AD42-DCD0A14E194D}"/>
   </bookViews>
@@ -40,23 +40,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="41">
   <si>
     <t>Reference</t>
   </si>
   <si>
-    <t>Dynamic perspective</t>
-  </si>
-  <si>
     <t>Distributional assumptions, sample of reject region or experts judgement</t>
   </si>
   <si>
-    <t>Concludes RI can (reliably) work?</t>
-  </si>
-  <si>
-    <t>Only with full sample of reject region</t>
-  </si>
-  <si>
     <t>Estimation of $p(x)$ for further usage in EM based methods</t>
   </si>
   <si>
@@ -72,9 +63,6 @@
     <t>HandHanley1993CanRIWork</t>
   </si>
   <si>
-    <t>Reliability of causality and dimensionality</t>
-  </si>
-  <si>
     <t>Knowledge and existence of causal non-cyclic relationships between features</t>
   </si>
   <si>
@@ -90,12 +78,6 @@
     <t>Rejects guide the decision boundary through low density regions in the features space</t>
   </si>
   <si>
-    <t>High dimensional feature space problematic</t>
-  </si>
-  <si>
-    <t>Yes, evaluation method is unreliable</t>
-  </si>
-  <si>
     <t>Low density regions of features space aligned with known labels separation</t>
   </si>
   <si>
@@ -105,27 +87,15 @@
     <t>Label missingness be independent across observations</t>
   </si>
   <si>
-    <t>Independence condition is illogical in dynamic context, numerical problems</t>
-  </si>
-  <si>
     <t>Estimation of unconditional means of features and probability of reject</t>
   </si>
   <si>
-    <t>Yes, in theoretical and simulation based results</t>
-  </si>
-  <si>
     <t>Banasik01032010</t>
   </si>
   <si>
-    <t>No, maybe with high rejection rates</t>
-  </si>
-  <si>
     <t>Augmentation via reweighting using accepts rejects model</t>
   </si>
   <si>
-    <t>Augmentation is not adequate for RI</t>
-  </si>
-  <si>
     <t>RI approach</t>
   </si>
   <si>
@@ -138,31 +108,61 @@
     <t>Accept reject model estimable</t>
   </si>
   <si>
-    <t>Assumptions explicit?</t>
-  </si>
-  <si>
-    <t>Theoretical/heuristic justification?</t>
-  </si>
-  <si>
-    <t>Infers Rejects label for evaluation?</t>
-  </si>
-  <si>
-    <t>Type of result</t>
-  </si>
-  <si>
-    <t>Theoretical</t>
-  </si>
-  <si>
-    <t>Empirical</t>
-  </si>
-  <si>
-    <t>Theoretical and simulation</t>
+    <t>Anderson2019BayesianNetForRI</t>
+  </si>
+  <si>
+    <t>LiEtAl2017SemisupervisedSVM</t>
+  </si>
+  <si>
+    <t>BuckerEtAl2013MNARRI</t>
   </si>
   <si>
     <t>Yes</t>
   </si>
   <si>
     <t>No</t>
+  </si>
+  <si>
+    <t>Result type</t>
+  </si>
+  <si>
+    <t>Does RI work?</t>
+  </si>
+  <si>
+    <t>Only with labeled rejects' smaple</t>
+  </si>
+  <si>
+    <t>Augmentation inadequate for RI</t>
+  </si>
+  <si>
+    <t>High dimensional feature space</t>
+  </si>
+  <si>
+    <t>Reliability of causality, dimensionality</t>
+  </si>
+  <si>
+    <t>Dynamic persp.</t>
+  </si>
+  <si>
+    <t>Theor.</t>
+  </si>
+  <si>
+    <t>Emp.</t>
+  </si>
+  <si>
+    <t>Theor., sim.</t>
+  </si>
+  <si>
+    <t>Theo./ heur. justified?</t>
+  </si>
+  <si>
+    <t>Assump. explicit?</t>
+  </si>
+  <si>
+    <t>Infers Rejects' label for eval?</t>
+  </si>
+  <si>
+    <t>Independence condition\footnote{The condition comes from the cited paper \cite{BuckerKramer2011} in the proof} illogical in dynamic context, numerical problems</t>
   </si>
 </sst>
 </file>
@@ -206,10 +206,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -565,74 +568,74 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="C1" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D1" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J1" t="s">
         <v>33</v>
-      </c>
-      <c r="F1" t="s">
-        <v>34</v>
-      </c>
-      <c r="G1" t="s">
-        <v>35</v>
-      </c>
-      <c r="H1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I1" t="s">
-        <v>6</v>
-      </c>
-      <c r="J1" t="s">
-        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2" t="b">
         <v>1</v>
       </c>
-      <c r="E2" t="b">
+      <c r="E2" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>40</v>
+      <c r="F2" t="b">
+        <v>0</v>
       </c>
       <c r="G2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J2" t="b">
+      <c r="J2" s="1" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>12</v>
-      </c>
       <c r="C3" s="2" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D3" t="b">
         <v>1</v>
@@ -640,17 +643,17 @@
       <c r="E3" t="b">
         <v>0</v>
       </c>
-      <c r="F3" t="s">
-        <v>40</v>
+      <c r="F3" s="1" t="b">
+        <v>0</v>
       </c>
       <c r="G3" t="s">
-        <v>37</v>
-      </c>
-      <c r="H3" t="s">
-        <v>13</v>
+        <v>35</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="J3" s="1" t="b">
         <v>0</v>
@@ -658,45 +661,45 @@
     </row>
     <row r="4" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G4" t="s">
+        <v>35</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>14</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" t="b">
-        <v>0</v>
-      </c>
-      <c r="E4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F4" t="s">
-        <v>39</v>
-      </c>
-      <c r="G4" t="s">
-        <v>37</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>20</v>
       </c>
       <c r="D5" t="b">
         <v>1</v>
@@ -704,31 +707,31 @@
       <c r="E5" t="b">
         <v>1</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H5" t="s">
+        <v>25</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="G5" t="s">
-        <v>38</v>
-      </c>
-      <c r="H5" t="s">
-        <v>23</v>
-      </c>
-      <c r="I5" s="2" t="s">
+      <c r="J5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>21</v>
-      </c>
-      <c r="J5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>24</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>31</v>
       </c>
       <c r="D6" t="b">
         <v>1</v>
@@ -736,17 +739,17 @@
       <c r="E6" t="b">
         <v>1</v>
       </c>
-      <c r="F6" t="s">
-        <v>40</v>
+      <c r="F6" t="b">
+        <v>0</v>
       </c>
       <c r="G6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J6" t="b">
         <v>0</v>
@@ -755,11 +758,18 @@
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
     </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C9" s="1"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="D10" s="1"/>
+    </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="E11" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -776,32 +786,32 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/thesis/data/table_literature_review.xlsx
+++ b/thesis/data/table_literature_review.xlsx
@@ -8,13 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mateo\Documents\Universidad\Master\Thesis\BEReBASL\thesis\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82B1D8F4-4D95-4C80-9875-71E7B245E65D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B2CA311-2D5D-4CF8-A87F-C14458726491}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D47D74D5-B8DF-4140-AD42-DCD0A14E194D}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
-    <sheet name="Hoja2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="68">
   <si>
     <t>Reference</t>
   </si>
@@ -57,57 +56,24 @@
     <t>Economic costs of sample</t>
   </si>
   <si>
-    <t>Anderson2019_BayesianNetForRI</t>
-  </si>
-  <si>
     <t>HandHanley1993CanRIWork</t>
   </si>
   <si>
     <t>Knowledge and existence of causal non-cyclic relationships between features</t>
   </si>
   <si>
-    <t>Extrapolation to rejects through bayesian network, then build scorecard on augemented sample</t>
-  </si>
-  <si>
     <t>Moderately</t>
   </si>
   <si>
-    <t>Li_et_al_2017_semisupervised_svm</t>
-  </si>
-  <si>
-    <t>Rejects guide the decision boundary through low density regions in the features space</t>
-  </si>
-  <si>
-    <t>Low density regions of features space aligned with known labels separation</t>
-  </si>
-  <si>
-    <t>Bucker_etal_2013_MNAR_RI</t>
-  </si>
-  <si>
-    <t>Label missingness be independent across observations</t>
-  </si>
-  <si>
-    <t>Estimation of unconditional means of features and probability of reject</t>
-  </si>
-  <si>
     <t>Banasik01032010</t>
   </si>
   <si>
-    <t>Augmentation via reweighting using accepts rejects model</t>
-  </si>
-  <si>
-    <t>RI approach</t>
-  </si>
-  <si>
     <t>RI Approach</t>
   </si>
   <si>
     <t>Key identifying assumptions</t>
   </si>
   <si>
-    <t>Accept reject model estimable</t>
-  </si>
-  <si>
     <t>Anderson2019BayesianNetForRI</t>
   </si>
   <si>
@@ -144,15 +110,9 @@
     <t>Dynamic persp.</t>
   </si>
   <si>
-    <t>Theor.</t>
-  </si>
-  <si>
     <t>Emp.</t>
   </si>
   <si>
-    <t>Theor., sim.</t>
-  </si>
-  <si>
     <t>Theo./ heur. justified?</t>
   </si>
   <si>
@@ -163,6 +123,126 @@
   </si>
   <si>
     <t>Independence condition\footnote{The condition comes from the cited paper \cite{BuckerKramer2011} in the proof} illogical in dynamic context, numerical problems</t>
+  </si>
+  <si>
+    <t>Theo.</t>
+  </si>
+  <si>
+    <t>Theo., sim.</t>
+  </si>
+  <si>
+    <t>BanasikCrook2003SampleSelBias</t>
+  </si>
+  <si>
+    <t>Emp., sim.</t>
+  </si>
+  <si>
+    <t>Moderately if MNAR and conservative FI</t>
+  </si>
+  <si>
+    <t>Errors in modelled equations are correlated, knowledge of relevant variables</t>
+  </si>
+  <si>
+    <t>Bivariate Probit for PD and AR equations (BVP)</t>
+  </si>
+  <si>
+    <t>BVP, Augmentation and BVP with Augmentation</t>
+  </si>
+  <si>
+    <t>Accept reject model estimable, enough rare accepts to correct</t>
+  </si>
+  <si>
+    <t>Augmentation via reweighting using AR model</t>
+  </si>
+  <si>
+    <t>Identification of AR and PD equations, correlation between their errors being $&gt;0$</t>
+  </si>
+  <si>
+    <t>No, worse than only accepts</t>
+  </si>
+  <si>
+    <t>bansikCrook2007</t>
+  </si>
+  <si>
+    <t>CrookBanasik2004DoesRIimprove</t>
+  </si>
+  <si>
+    <t>Augmentation and Extrapolation</t>
+  </si>
+  <si>
+    <t>Extrapolation to rejects through bayesian network, then build scorecard on extrapolated sample</t>
+  </si>
+  <si>
+    <t>MancisdorEtAl2020DeepGenMForRI</t>
+  </si>
+  <si>
+    <t>Use a generative model with latent features $L$\footnote{They use $z$ as letter in the paper, but here that letter stands for the acceptance status and is thus changed} in form $Y \to L \to X$, where rejects are used to train the encoder of $X$ onto $L$, while being tied by the accepts to be consistent in class conditional prior assumptions $Y \to L$</t>
+  </si>
+  <si>
+    <t>Causal markov chain $Y \to Z \to X$, distributional assumptions on certain marginals of the system. Implicitly MAR\footnote{Effecitvely they model $P(Y | X, Z=a) = P(Y | X, Z = r)$ assumption}</t>
+  </si>
+  <si>
+    <t>Numerical stability, sensitivity to initial weights, explainability for regulatory</t>
+  </si>
+  <si>
+    <t>ShengEtAl2024RICostSenstiveJointDistAdap</t>
+  </si>
+  <si>
+    <t>Semisupervised SVM (S3VM): Rejects guide the decision boundary through low density regions in the features space</t>
+  </si>
+  <si>
+    <t>Estimation of unconditional means of features and probability of reject for generative model</t>
+  </si>
+  <si>
+    <t>For Joint Distribution Adaptation (JDA) to reduce dist. Differences between rejects and accepts, and for cost sensitive S3VM</t>
+  </si>
+  <si>
+    <t>Low density regions of features space aligned with known labels separation, MAR</t>
+  </si>
+  <si>
+    <t>Label missingness be independent across observations, MNAR</t>
+  </si>
+  <si>
+    <t>JDA can turn MNAR into MAR in latent space, low density separability assumption</t>
+  </si>
+  <si>
+    <t>JDA depends on high feature dimensionality, computational costs, explaniability</t>
+  </si>
+  <si>
+    <t>Feelders2000RIMixtureModels</t>
+  </si>
+  <si>
+    <t>MAR</t>
+  </si>
+  <si>
+    <t>EM algorithm, for rejects explicit expectation over the two classes weighted by the posterior</t>
+  </si>
+  <si>
+    <t>Sim.</t>
+  </si>
+  <si>
+    <t>Parameters scale quadratically with features dimensionality, doubtful whether the DGP can be so simple and unrealistic acceptance rule</t>
+  </si>
+  <si>
+    <t>Yes, for small samples and feature space</t>
+  </si>
+  <si>
+    <t>BoyesHoffmann1985HeckmanInCreditScoring</t>
+  </si>
+  <si>
+    <t>MNAR, Bivariate Probit assumptions, FI are rational and may seek to optimize for high balances</t>
+  </si>
+  <si>
+    <t>Emp. and simulation</t>
+  </si>
+  <si>
+    <t>Unclear, only comparision of decision differences presented</t>
+  </si>
+  <si>
+    <t>Data required for proposed ``behavioral" credit scoring model is hard to obtain</t>
+  </si>
+  <si>
+    <t>Heckman type PD/AR estimation with augmentation where weights are proportional to population frequencies for behavioral scoring model</t>
   </si>
 </sst>
 </file>
@@ -549,10 +629,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8852FF5C-5175-44DA-A620-18833DBB2C7A}">
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="28.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="38.33203125" customWidth="1"/>
     <col min="2" max="3" width="28.21875" customWidth="1"/>
     <col min="4" max="4" width="21.88671875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="21.6640625" customWidth="1"/>
@@ -568,36 +648,36 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C1" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D1" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="E1" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="F1" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="G1" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="H1" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="I1" t="s">
         <v>3</v>
       </c>
       <c r="J1" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>2</v>
@@ -615,10 +695,10 @@
         <v>0</v>
       </c>
       <c r="G2" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>4</v>
@@ -629,63 +709,63 @@
     </row>
     <row r="3" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F3" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F3" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="G3" t="s">
-        <v>35</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>9</v>
-      </c>
       <c r="I3" s="2" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="J3" s="1" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G4" t="s">
         <v>23</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" t="b">
-        <v>0</v>
-      </c>
-      <c r="E4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G4" t="s">
-        <v>35</v>
-      </c>
       <c r="H4" s="2" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="J4" t="b">
         <v>0</v>
@@ -693,31 +773,31 @@
     </row>
     <row r="5" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G5" t="s">
+        <v>29</v>
+      </c>
+      <c r="H5" t="s">
         <v>14</v>
       </c>
-      <c r="D5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="H5" t="s">
-        <v>25</v>
-      </c>
       <c r="I5" s="2" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="J5" t="b">
         <v>0</v>
@@ -725,13 +805,13 @@
     </row>
     <row r="6" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="D6" t="b">
         <v>1</v>
@@ -743,78 +823,254 @@
         <v>0</v>
       </c>
       <c r="G6" t="s">
+        <v>23</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E7" t="b">
+        <v>1</v>
+      </c>
+      <c r="F7" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G7" t="s">
+        <v>31</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="J7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="H6" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="J6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A8" s="1"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="C9" s="1"/>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="D10" s="1"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="E11" s="1"/>
+      <c r="C8" s="2" t="str">
+        <f>"For BVP like in \textcite{"&amp;A7&amp;"}. For Augmentation like \textcite{"&amp;A6&amp;"}"</f>
+        <v>For BVP like in \textcite{BanasikCrook2003SampleSelBias}. For Augmentation like \textcite{Banasik01032010}</v>
+      </c>
+      <c r="D8" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E8" t="b">
+        <v>1</v>
+      </c>
+      <c r="F8" t="b">
+        <v>0</v>
+      </c>
+      <c r="G8" t="s">
+        <v>23</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I8" s="2" t="str">
+        <f>"Also alike to \textcite{"&amp;A7&amp;"} and \textcite{"&amp;A6&amp;"}"</f>
+        <v>Also alike to \textcite{BanasikCrook2003SampleSelBias} and \textcite{Banasik01032010}</v>
+      </c>
+      <c r="J8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C9" s="2" t="str">
+        <f>"For Augmentation like \textcite{"&amp;A6&amp;"}, for extrapolation $\mathbb{P}(Y=g | X)$ similar in accepts and rejects"</f>
+        <v>For Augmentation like \textcite{Banasik01032010}, for extrapolation $\mathbb{P}(Y=g | X)$ similar in accepts and rejects</v>
+      </c>
+      <c r="D9" t="b">
+        <v>1</v>
+      </c>
+      <c r="E9" t="b">
+        <v>1</v>
+      </c>
+      <c r="F9" t="b">
+        <v>0</v>
+      </c>
+      <c r="G9" t="s">
+        <v>23</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I9" s="1" t="str">
+        <f>"Like \textcite{"&amp;A7&amp;"} and \textcite{"&amp;A6&amp;"}"</f>
+        <v>Like \textcite{BanasikCrook2003SampleSelBias} and \textcite{Banasik01032010}</v>
+      </c>
+      <c r="J9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>44</v>
+      </c>
+      <c r="B10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D10" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E10" t="b">
+        <v>0</v>
+      </c>
+      <c r="F10" t="b">
+        <v>0</v>
+      </c>
+      <c r="G10" t="s">
+        <v>23</v>
+      </c>
+      <c r="H10" t="s">
+        <v>14</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="J10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>48</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D11" t="b">
+        <v>1</v>
+      </c>
+      <c r="E11" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="F11" t="b">
+        <v>0</v>
+      </c>
+      <c r="G11" t="s">
+        <v>23</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="J11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="72" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D12" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E12" t="b">
+        <v>1</v>
+      </c>
+      <c r="F12" t="b">
+        <v>0</v>
+      </c>
+      <c r="G12" t="s">
+        <v>59</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="J12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="72" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>62</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C13" t="s">
+        <v>63</v>
+      </c>
+      <c r="D13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E13" t="b">
+        <v>1</v>
+      </c>
+      <c r="F13" t="b">
+        <v>0</v>
+      </c>
+      <c r="G13" t="s">
+        <v>64</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="J13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J14" s="1"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C15" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD0A6221-C3E5-43E7-83EA-25D1D90EAB9E}">
-  <dimension ref="A1:B6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="29.33203125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/thesis/data/table_literature_review.xlsx
+++ b/thesis/data/table_literature_review.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mateo\Documents\Universidad\Master\Thesis\BEReBASL\thesis\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B2CA311-2D5D-4CF8-A87F-C14458726491}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A102D66-D15B-4679-8404-CAC11A6F8A56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D47D74D5-B8DF-4140-AD42-DCD0A14E194D}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="101">
   <si>
     <t>Reference</t>
   </si>
@@ -101,9 +101,6 @@
     <t>Augmentation inadequate for RI</t>
   </si>
   <si>
-    <t>High dimensional feature space</t>
-  </si>
-  <si>
     <t>Reliability of causality, dimensionality</t>
   </si>
   <si>
@@ -243,6 +240,109 @@
   </si>
   <si>
     <t>Heckman type PD/AR estimation with augmentation where weights are proportional to population frequencies for behavioral scoring model</t>
+  </si>
+  <si>
+    <t>ChenAstebro2010RIBoundCollapseBayesian</t>
+  </si>
+  <si>
+    <t>Bayesian Bound and Collapse method on multinomial over combinations of scoring, repayment and missingness indicator, to then extrapolate to obtain complete sample</t>
+  </si>
+  <si>
+    <t>MNAR, single cut-off point for whole sample, probability of reject estimable</t>
+  </si>
+  <si>
+    <t>Emp. with simulated cutoff</t>
+  </si>
+  <si>
+    <t>Yes, measured on artificial reject/accept region of past credits</t>
+  </si>
+  <si>
+    <t>Data needed scales strongly with range of scores, unclear how the data is MNAR</t>
+  </si>
+  <si>
+    <t>ElAnnas2022SemisupervisedAH</t>
+  </si>
+  <si>
+    <t>High dimensional feature space, handling large amounts of data</t>
+  </si>
+  <si>
+    <t>Semisupervised hidden markov model, where a sequential model along the (binned) features is modeled with two hidden states representing bad and good outcomes. The hidden states are semantically anchored at the beginning with a maximum likelihood estimation of transition parameters in the markov chain. The Rejects are used to finetune the transition probabilities in an unsupervised manner</t>
+  </si>
+  <si>
+    <t>A Markov Chain along the features in a specific order is sensible and can be meaningfully tied to hidden states, the rejects further do not break up the semantics of the hidden states.</t>
+  </si>
+  <si>
+    <t>Rejects and Accepts must have the same available features, unclear how to define the order of features in chain</t>
+  </si>
+  <si>
+    <t>KangEtAl2021GraphBasedSemiRI</t>
+  </si>
+  <si>
+    <t>Emp. Including A/B testing</t>
+  </si>
+  <si>
+    <t>Computational costs, Borderline SMOTE scales bad with features dimension, explainability for distance metric with discrete features</t>
+  </si>
+  <si>
+    <t>Semisupervised label propagation: use fully connected graph over all observations, where observations alike form clusters that are assigned a label according to known labels in the cluster, regularized to avoid overfitting through penalization of deviation of initial supervised only label setting and controling for accepts class imbalance through Borderline-SMOTE. Clusters are calculated through mahalanobis distance</t>
+  </si>
+  <si>
+    <t>kozdoi_et_al_BE_BASL</t>
+  </si>
+  <si>
+    <t>Rejects closest to accepts share labels, larger manifolds with common labels concentrations also share labels. Upsampled points on the borderline between minority and majority contain more valuable information</t>
+  </si>
+  <si>
+    <t>Bayesian Evaluation: Use random conditional bernoulli based extrapolation on evaluation set iteratively to get bayesian metric. For inference: iteratively partially extrapolate to generate high confidence rejects' labels to generate larger complete data for training scorecard</t>
+  </si>
+  <si>
+    <t>MAR or MNAR data, partial debiasing is more useful than extrapolating all rejects, rejects contain higher bad rates, posterior estimate can be calibrated</t>
+  </si>
+  <si>
+    <t>Sim. and Emp.</t>
+  </si>
+  <si>
+    <t>Yes for evaluation, estimation also under specific conditions</t>
+  </si>
+  <si>
+    <t>BASL: sensitivity to class imbalance, understanding when it is worthwhile using it</t>
+  </si>
+  <si>
+    <t>MaldonadoParedes2010SemiSupSVM</t>
+  </si>
+  <si>
+    <t>SVM with penalization term for low confident predictions (low density region) on unlabeld data as learner for self-training</t>
+  </si>
+  <si>
+    <t>Linear classification boundaries, low density assumption in unlabeled data, accurate classifier per iteration in self-training</t>
+  </si>
+  <si>
+    <t>Sim. And Emp.</t>
+  </si>
+  <si>
+    <t>Yes in sim., in emp. also with artificial rejects\footnote{meaning: rejects among the accepted clients in the samples}</t>
+  </si>
+  <si>
+    <t>Linearity constraint, high dimensional feature space, handling large amounts of data</t>
+  </si>
+  <si>
+    <t>XiaEtAl2018RIPesimisticLikelihood</t>
+  </si>
+  <si>
+    <t>Contrastive Pessimistic Likelihood (CPLE) with LigthGBM, where the CPLE objective is optimized with fully extrapolated rejects, which are weighted by their PD</t>
+  </si>
+  <si>
+    <t>From CPLE framework: well-defined likelihood, calibrated PD-estimator over reject region, same features available for rejects and accepts, MNAR
+From LightGBM usage: pruning breaks self-reinforcing error loop and PD estimation is almost continuous</t>
+  </si>
+  <si>
+    <t>Computational costs scale with reject rate, ensuring non-overfitted well calibrated classifier</t>
+  </si>
+  <si>
+    <t>Yes, on holdout accepts</t>
+  </si>
+  <si>
+    <t>Moderately based on accepts only eval.</t>
   </si>
 </sst>
 </file>
@@ -629,7 +729,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8852FF5C-5175-44DA-A620-18833DBB2C7A}">
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="38.33203125" customWidth="1"/>
@@ -654,13 +754,13 @@
         <v>10</v>
       </c>
       <c r="D1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" t="s">
         <v>25</v>
-      </c>
-      <c r="E1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F1" t="s">
-        <v>26</v>
       </c>
       <c r="G1" t="s">
         <v>16</v>
@@ -672,7 +772,7 @@
         <v>3</v>
       </c>
       <c r="J1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
@@ -695,7 +795,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>18</v>
@@ -712,7 +812,7 @@
         <v>11</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>6</v>
@@ -727,13 +827,13 @@
         <v>0</v>
       </c>
       <c r="G3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J3" s="1" t="b">
         <v>0</v>
@@ -744,10 +844,10 @@
         <v>12</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D4" t="b">
         <v>0</v>
@@ -759,13 +859,13 @@
         <v>1</v>
       </c>
       <c r="G4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>20</v>
+        <v>74</v>
       </c>
       <c r="J4" t="b">
         <v>0</v>
@@ -776,10 +876,10 @@
         <v>13</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D5" t="b">
         <v>1</v>
@@ -791,13 +891,13 @@
         <v>0</v>
       </c>
       <c r="G5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H5" t="s">
         <v>14</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J5" t="b">
         <v>0</v>
@@ -808,10 +908,10 @@
         <v>8</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D6" t="b">
         <v>1</v>
@@ -823,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="G6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>19</v>
@@ -837,31 +937,31 @@
     </row>
     <row r="7" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E7" t="b">
+        <v>1</v>
+      </c>
+      <c r="F7" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G7" t="s">
         <v>30</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D7" t="b">
-        <v>1</v>
-      </c>
-      <c r="E7" t="b">
-        <v>1</v>
-      </c>
-      <c r="F7" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="G7" t="s">
+      <c r="H7" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="H7" s="2" t="s">
-        <v>32</v>
-      </c>
       <c r="I7" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J7" t="b">
         <v>0</v>
@@ -869,10 +969,10 @@
     </row>
     <row r="8" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C8" s="2" t="str">
         <f>"For BVP like in \textcite{"&amp;A7&amp;"}. For Augmentation like \textcite{"&amp;A6&amp;"}"</f>
@@ -888,7 +988,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>15</v>
@@ -903,10 +1003,10 @@
     </row>
     <row r="9" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>40</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>42</v>
       </c>
       <c r="C9" s="2" t="str">
         <f>"For Augmentation like \textcite{"&amp;A6&amp;"}, for extrapolation $\mathbb{P}(Y=g | X)$ similar in accepts and rejects"</f>
@@ -922,7 +1022,7 @@
         <v>0</v>
       </c>
       <c r="G9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>15</v>
@@ -937,14 +1037,14 @@
     </row>
     <row r="10" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10" t="s">
         <v>44</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>46</v>
-      </c>
       <c r="D10" s="1" t="b">
         <v>1</v>
       </c>
@@ -955,13 +1055,13 @@
         <v>0</v>
       </c>
       <c r="G10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H10" t="s">
         <v>14</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J10" t="b">
         <v>0</v>
@@ -969,13 +1069,13 @@
     </row>
     <row r="11" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D11" t="b">
         <v>1</v>
@@ -987,13 +1087,13 @@
         <v>0</v>
       </c>
       <c r="G11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J11" t="b">
         <v>0</v>
@@ -1001,31 +1101,31 @@
     </row>
     <row r="12" spans="1:10" ht="72" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="D12" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E12" t="b">
+        <v>1</v>
+      </c>
+      <c r="F12" t="b">
+        <v>0</v>
+      </c>
+      <c r="G12" t="s">
         <v>58</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="D12" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="E12" t="b">
-        <v>1</v>
-      </c>
-      <c r="F12" t="b">
-        <v>0</v>
-      </c>
-      <c r="G12" t="s">
+      <c r="H12" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="I12" s="2" t="s">
         <v>59</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>60</v>
       </c>
       <c r="J12" t="b">
         <v>0</v>
@@ -1033,41 +1133,227 @@
     </row>
     <row r="13" spans="1:10" ht="72" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
+        <v>61</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C13" t="s">
         <v>62</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="D13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E13" t="b">
+        <v>1</v>
+      </c>
+      <c r="F13" t="b">
+        <v>0</v>
+      </c>
+      <c r="G13" t="s">
+        <v>63</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="J13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
         <v>67</v>
       </c>
-      <c r="C13" t="s">
-        <v>63</v>
-      </c>
-      <c r="D13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E13" t="b">
-        <v>1</v>
-      </c>
-      <c r="F13" t="b">
-        <v>0</v>
-      </c>
-      <c r="G13" t="s">
-        <v>64</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="J13" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="J14" s="1"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="C15" s="1"/>
+      <c r="B14" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C14" t="s">
+        <v>69</v>
+      </c>
+      <c r="D14" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="E14" t="b">
+        <v>1</v>
+      </c>
+      <c r="F14" t="b">
+        <v>0</v>
+      </c>
+      <c r="G14" t="s">
+        <v>70</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="J14" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="187.2" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D15" t="b">
+        <v>0</v>
+      </c>
+      <c r="E15" t="b">
+        <v>0</v>
+      </c>
+      <c r="F15" t="b">
+        <v>1</v>
+      </c>
+      <c r="G15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="J15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="201.6" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D16" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E16" t="b">
+        <v>1</v>
+      </c>
+      <c r="F16" t="b">
+        <v>0</v>
+      </c>
+      <c r="G16" t="s">
+        <v>79</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="J16" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D17" t="b">
+        <v>1</v>
+      </c>
+      <c r="E17" t="b">
+        <v>1</v>
+      </c>
+      <c r="F17" t="b">
+        <v>0</v>
+      </c>
+      <c r="G17" t="s">
+        <v>86</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="J17" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="72" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>89</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D18" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E18" t="b">
+        <v>1</v>
+      </c>
+      <c r="F18" t="b">
+        <v>0</v>
+      </c>
+      <c r="G18" t="s">
+        <v>92</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="J18" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>95</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="D19" t="b">
+        <v>0</v>
+      </c>
+      <c r="E19" t="b">
+        <v>1</v>
+      </c>
+      <c r="F19" t="b">
+        <v>0</v>
+      </c>
+      <c r="G19" t="s">
+        <v>22</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="J19" s="1" t="b">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/thesis/data/table_literature_review.xlsx
+++ b/thesis/data/table_literature_review.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mateo\Documents\Universidad\Master\Thesis\BEReBASL\thesis\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A102D66-D15B-4679-8404-CAC11A6F8A56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDF357FC-D624-43DA-94D6-CE7D1BE8D831}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D47D74D5-B8DF-4140-AD42-DCD0A14E194D}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="111">
   <si>
     <t>Reference</t>
   </si>
@@ -222,9 +222,6 @@
   </si>
   <si>
     <t>Yes, for small samples and feature space</t>
-  </si>
-  <si>
-    <t>BoyesHoffmann1985HeckmanInCreditScoring</t>
   </si>
   <si>
     <t>MNAR, Bivariate Probit assumptions, FI are rational and may seek to optimize for high balances</t>
@@ -343,6 +340,39 @@
   </si>
   <si>
     <t>Moderately based on accepts only eval.</t>
+  </si>
+  <si>
+    <t>ShenEtAl2020ThreeStageRI</t>
+  </si>
+  <si>
+    <t>Most similar Rejects selected through 3-way-decision (3WD) theory based on Mahalanobis distance (MD) to accepts are used jointly with accepts to learn higher level features representations of through Self-Thought-Learning (STL). This representation is used for further supervised learning on accepts</t>
+  </si>
+  <si>
+    <t>STL will produce features better aligned for credit scoring using \textit{any downstream algorithm} as it does not assume equal distributions of accepts and rejects. MD serves as proxy to prevent negative transferin STL by including only rejects features alike to the accepts, which allows to induce they assume the data is not MNAR. MD is suitable for a mix of contiguous, binary and categorical data</t>
+  </si>
+  <si>
+    <t>Yes, on holdout accepts\footnote{They did however not check if the improvement comes from higher feature representation learning or from RI}</t>
+  </si>
+  <si>
+    <t>Extremeley High computational costs due to 3WD, explainability and credibility</t>
+  </si>
+  <si>
+    <t>A Kernel-free Fuzzy Quadratic Surface SVM (FQSSVM) approach consisting of: (1) initial separation to compute distance metrics; (2) outlier detection using local neighborhood affinity to eliminate default outliers; (3) a fuzzy weighting scheme based on class centers, local hesitation, and proximity to the boundary; and (4) convex FQSSVM optimization on both accepted and weighted, temporarily labeled rejected samples</t>
+  </si>
+  <si>
+    <t>BoyesEtAl1989EconxAnalysis</t>
+  </si>
+  <si>
+    <t>MAR DGP, all rejects as bad appropiate for initial separation. Accepted default borrowers with excellent attributes are ``outliers" (accidental defaults) whose elimination improves classification accuracy. Rejects positioned near the initial separating boundary represent potential good borrowers</t>
+  </si>
+  <si>
+    <t>Yes, on evaluated sets</t>
+  </si>
+  <si>
+    <t>High dependency on heuristic parameter selection</t>
+  </si>
+  <si>
+    <t>TianEtAl2018RIKernelFreeFuzzySVM</t>
   </si>
 </sst>
 </file>
@@ -729,7 +759,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8852FF5C-5175-44DA-A620-18833DBB2C7A}">
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="38.33203125" customWidth="1"/>
@@ -865,7 +895,7 @@
         <v>14</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J4" t="b">
         <v>0</v>
@@ -1133,31 +1163,31 @@
     </row>
     <row r="13" spans="1:10" ht="72" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
+        <v>106</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C13" t="s">
         <v>61</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C13" t="s">
+      <c r="D13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E13" t="b">
+        <v>1</v>
+      </c>
+      <c r="F13" t="b">
+        <v>0</v>
+      </c>
+      <c r="G13" t="s">
         <v>62</v>
       </c>
-      <c r="D13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E13" t="b">
-        <v>1</v>
-      </c>
-      <c r="F13" t="b">
-        <v>0</v>
-      </c>
-      <c r="G13" t="s">
+      <c r="H13" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="H13" s="2" t="s">
+      <c r="I13" s="2" t="s">
         <v>64</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>65</v>
       </c>
       <c r="J13" t="b">
         <v>0</v>
@@ -1165,31 +1195,31 @@
     </row>
     <row r="14" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>66</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="C14" t="s">
         <v>68</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="E14" t="b">
+        <v>1</v>
+      </c>
+      <c r="F14" t="b">
+        <v>0</v>
+      </c>
+      <c r="G14" t="s">
         <v>69</v>
       </c>
-      <c r="D14" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="E14" t="b">
-        <v>1</v>
-      </c>
-      <c r="F14" t="b">
-        <v>0</v>
-      </c>
-      <c r="G14" t="s">
+      <c r="H14" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="H14" s="2" t="s">
+      <c r="I14" s="2" t="s">
         <v>71</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>72</v>
       </c>
       <c r="J14" s="1" t="b">
         <v>0</v>
@@ -1197,13 +1227,13 @@
     </row>
     <row r="15" spans="1:10" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>75</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>76</v>
       </c>
       <c r="D15" t="b">
         <v>0</v>
@@ -1218,10 +1248,10 @@
         <v>22</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J15" t="b">
         <v>0</v>
@@ -1229,31 +1259,31 @@
     </row>
     <row r="16" spans="1:10" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D16" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E16" t="b">
+        <v>1</v>
+      </c>
+      <c r="F16" t="b">
+        <v>0</v>
+      </c>
+      <c r="G16" t="s">
         <v>78</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="D16" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="E16" t="b">
-        <v>1</v>
-      </c>
-      <c r="F16" t="b">
-        <v>0</v>
-      </c>
-      <c r="G16" t="s">
-        <v>79</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J16" t="b">
         <v>0</v>
@@ -1261,31 +1291,31 @@
     </row>
     <row r="17" spans="1:10" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B17" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="D17" t="b">
+        <v>1</v>
+      </c>
+      <c r="E17" t="b">
+        <v>1</v>
+      </c>
+      <c r="F17" t="b">
+        <v>0</v>
+      </c>
+      <c r="G17" t="s">
         <v>85</v>
       </c>
-      <c r="D17" t="b">
-        <v>1</v>
-      </c>
-      <c r="E17" t="b">
-        <v>1</v>
-      </c>
-      <c r="F17" t="b">
-        <v>0</v>
-      </c>
-      <c r="G17" t="s">
+      <c r="H17" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="H17" s="2" t="s">
+      <c r="I17" s="2" t="s">
         <v>87</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>88</v>
       </c>
       <c r="J17" t="b">
         <v>0</v>
@@ -1293,31 +1323,31 @@
     </row>
     <row r="18" spans="1:10" ht="72" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
+        <v>88</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="C18" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="D18" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E18" t="b">
+        <v>1</v>
+      </c>
+      <c r="F18" t="b">
+        <v>0</v>
+      </c>
+      <c r="G18" t="s">
         <v>91</v>
       </c>
-      <c r="D18" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="E18" t="b">
-        <v>1</v>
-      </c>
-      <c r="F18" t="b">
-        <v>0</v>
-      </c>
-      <c r="G18" t="s">
+      <c r="H18" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="H18" s="2" t="s">
+      <c r="I18" s="2" t="s">
         <v>93</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>94</v>
       </c>
       <c r="J18" t="b">
         <v>0</v>
@@ -1325,13 +1355,13 @@
     </row>
     <row r="19" spans="1:10" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
+        <v>94</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="C19" s="3" t="s">
         <v>96</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>97</v>
       </c>
       <c r="D19" t="b">
         <v>0</v>
@@ -1346,12 +1376,76 @@
         <v>22</v>
       </c>
       <c r="H19" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="J19" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="187.2" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
         <v>100</v>
       </c>
-      <c r="I19" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="J19" s="1" t="b">
+      <c r="B20" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="D20" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="E20" t="b">
+        <v>1</v>
+      </c>
+      <c r="F20" t="b">
+        <v>0</v>
+      </c>
+      <c r="G20" t="s">
+        <v>22</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="J20" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="201.6" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>110</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D21" t="b">
+        <v>0</v>
+      </c>
+      <c r="E21" t="b">
+        <v>1</v>
+      </c>
+      <c r="F21" t="b">
+        <v>1</v>
+      </c>
+      <c r="G21" t="s">
+        <v>22</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="I21" t="s">
+        <v>109</v>
+      </c>
+      <c r="J21" t="b">
         <v>0</v>
       </c>
     </row>

--- a/thesis/data/table_literature_review.xlsx
+++ b/thesis/data/table_literature_review.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mateo\Documents\Universidad\Master\Thesis\BEReBASL\thesis\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDF357FC-D624-43DA-94D6-CE7D1BE8D831}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A93948F-F040-4231-8E4A-4F2EE4B1FB38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D47D74D5-B8DF-4140-AD42-DCD0A14E194D}"/>
   </bookViews>
@@ -357,22 +357,22 @@
     <t>Extremeley High computational costs due to 3WD, explainability and credibility</t>
   </si>
   <si>
-    <t>A Kernel-free Fuzzy Quadratic Surface SVM (FQSSVM) approach consisting of: (1) initial separation to compute distance metrics; (2) outlier detection using local neighborhood affinity to eliminate default outliers; (3) a fuzzy weighting scheme based on class centers, local hesitation, and proximity to the boundary; and (4) convex FQSSVM optimization on both accepted and weighted, temporarily labeled rejected samples</t>
-  </si>
-  <si>
     <t>BoyesEtAl1989EconxAnalysis</t>
   </si>
   <si>
-    <t>MAR DGP, all rejects as bad appropiate for initial separation. Accepted default borrowers with excellent attributes are ``outliers" (accidental defaults) whose elimination improves classification accuracy. Rejects positioned near the initial separating boundary represent potential good borrowers</t>
-  </si>
-  <si>
-    <t>Yes, on evaluated sets</t>
-  </si>
-  <si>
-    <t>High dependency on heuristic parameter selection</t>
-  </si>
-  <si>
     <t>TianEtAl2018RIKernelFreeFuzzySVM</t>
+  </si>
+  <si>
+    <t>A Kernel-free Fuzzy Quadratic Surface SVM (FQSSVM) approach consisting of: initial FQSSVM-separation to compute eucl. distance metrics to boundary; outlier detection using local neighborhood affinity to eliminate default outliers with rejects seen as bads from here on; a fuzzy weighting scheme based on class centers, local hesitation, and proximity to the boundary, where potentially good rejects recieve small missclasification penalization weights; and convex FQSSVM optimization on both accepted and weighted, temporarily labeled rejected samples</t>
+  </si>
+  <si>
+    <t>Yes, with rejects' labels were (partially) inferred</t>
+  </si>
+  <si>
+    <t>MAR DGP, all rejects as bad appropiate for initial separation. Accepted default borrowers with excellent attributes are ``outliers" (accidental defaults) whose elimination improves classification accuracy\footnote{This assumption implies a series of assumptions alike to the model presented in \ref{sec-measure-theoretic-desc-ri-problem}}. Rejects positioned near the initial separating boundary represent potential good borrowers, meaning the separation boundary is assumed to be already near optimal. Quadratic surface a good approximator of ``any" separation boundary\footnote{Which cannot be, their argument on taylor approximation is taken to be too general}</t>
+  </si>
+  <si>
+    <t>Unclear dependency on heuristic distance measures, unclear whether results come from the inferred labels, explainability</t>
   </si>
 </sst>
 </file>
@@ -1163,7 +1163,7 @@
     </row>
     <row r="13" spans="1:10" ht="72" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>65</v>
@@ -1417,21 +1417,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="201.6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" ht="345.6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D21" t="b">
         <v>0</v>
       </c>
       <c r="E21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F21" t="b">
         <v>1</v>
@@ -1439,11 +1439,11 @@
       <c r="G21" t="s">
         <v>22</v>
       </c>
-      <c r="H21" s="2" t="s">
+      <c r="H21" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="I21" t="s">
-        <v>109</v>
+      <c r="I21" s="1" t="s">
+        <v>110</v>
       </c>
       <c r="J21" t="b">
         <v>0</v>

--- a/thesis/data/table_literature_review.xlsx
+++ b/thesis/data/table_literature_review.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mateo\Documents\Universidad\Master\Thesis\BEReBASL\thesis\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A93948F-F040-4231-8E4A-4F2EE4B1FB38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F721819-71F3-4893-B411-7FE9E5CA7FDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D47D74D5-B8DF-4140-AD42-DCD0A14E194D}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="126">
   <si>
     <t>Reference</t>
   </si>
@@ -225,9 +225,6 @@
   </si>
   <si>
     <t>MNAR, Bivariate Probit assumptions, FI are rational and may seek to optimize for high balances</t>
-  </si>
-  <si>
-    <t>Emp. and simulation</t>
   </si>
   <si>
     <t>Unclear, only comparision of decision differences presented</t>
@@ -373,6 +370,54 @@
   </si>
   <si>
     <t>Unclear dependency on heuristic distance measures, unclear whether results come from the inferred labels, explainability</t>
+  </si>
+  <si>
+    <t>Xia2019ANR</t>
+  </si>
+  <si>
+    <t>Kang2022CWGAN</t>
+  </si>
+  <si>
+    <t>ribeiro2025balancingperformancerejectinclusion</t>
+  </si>
+  <si>
+    <t>Moderately based on accepts only eval</t>
+  </si>
+  <si>
+    <t>Estimate Isolation Forest (IFO) on rejects to label them: outliers as goods, inliers as bad where this classification happens through heuristic setting of Contamination Rate (CR). Then LightGBM on rejects and accepts where missing values of rejects' features are set to 0 and all features are 0-1 normalized</t>
+  </si>
+  <si>
+    <t>Accurately estimating the true latent contamination rate (CR) of the rejects, as the optimal CR varies between datasets and heavily impacts model performanc</t>
+  </si>
+  <si>
+    <t>MNAR, acceptance decision process is very good: almost only bads are rejected, as IFO-uncommon rejects are expected to be good payers; bads among the rejects are homogenous. 0 imputation is good regardless the type of feature</t>
+  </si>
+  <si>
+    <t>Conditional Wasserstein Generative Adversarial Network with Gradient Penalty (CWGAN-GP) combined with Multi-Task Learning (MTL). First, CWGAN-GP models the complete population feature space using rejects with ``virtual labels''\footnote{The derivation or assignment mechanism for these virtual labels is not explicitly specified in the paper.} to generate synthetic defaults. Second, a multi-task network with shared embedding layers jointly optimizes default risk on the CWGAN-GP-rebalanced dataset and acceptance classification using the rejected features.</t>
+  </si>
+  <si>
+    <t>Likely MNAR\footnote{As they model explicitly the Accept/Reject decision, not explicitly formulated}. Same features among accepts and rejects. Virtual label mechanism for rejects does not bias the generative process and does not need weighting these observations. The same latent feature representations for rejects works for modeling GB and AR equations. That specific AR modeling alleviates the bias on GB.</t>
+  </si>
+  <si>
+    <t>On holdout accept: yes for rebalancing and moderately prediction\footnote{The greatest gain in prediction comes from the rebalancing, the MLT part was not benchmarked to other methods considering auxiliary tasks like Heckman's model}</t>
+  </si>
+  <si>
+    <t>Computational burden of training generative model, selecting the rate of generated samples, explainability</t>
+  </si>
+  <si>
+    <t>Confident Inlier Extrapolation (CI-EX): A semi-supervised framework that iteratively identifies non-outlier rejected samples per class using class-conditional Isolation Forest and assigns labels to the most confident candidates based on probabilities from a balanced classifier</t>
+  </si>
+  <si>
+    <t>Rejects are geomatric inliers relative to accepted samples and can be safely pseudo-labeled using classifier certainty. Iterative, controlled addition of confident inliers prevents catastrophic extrapolation drift. valuating RI solely on accepted test sets (via standard AUC) is fundamentally biased, requiring population/debiased metrics like Kickout and Area Under the Kickout (AUK)</t>
+  </si>
+  <si>
+    <t>Emp. and sim.</t>
+  </si>
+  <si>
+    <t>Moderately / Trade-off dependent</t>
+  </si>
+  <si>
+    <t>Managing the explicit trade-off between maximizing population debiasing (AUK) and maintaining accepted-set accuracy (AUC), alongside the computational overhead of multi-step iterative retraining</t>
   </si>
 </sst>
 </file>
@@ -419,10 +464,8 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -759,695 +802,793 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8852FF5C-5175-44DA-A620-18833DBB2C7A}">
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="38.33203125" customWidth="1"/>
-    <col min="2" max="3" width="28.21875" customWidth="1"/>
-    <col min="4" max="4" width="21.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.6640625" customWidth="1"/>
-    <col min="6" max="6" width="28.6640625" customWidth="1"/>
-    <col min="7" max="7" width="24.88671875" customWidth="1"/>
-    <col min="8" max="8" width="27.44140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="27.44140625" customWidth="1"/>
-    <col min="10" max="10" width="27.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="38.33203125" style="2" customWidth="1"/>
+    <col min="2" max="3" width="28.21875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="21.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.6640625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="28.6640625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="24.88671875" style="2" customWidth="1"/>
+    <col min="8" max="8" width="27.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="27.44140625" style="2" customWidth="1"/>
+    <col min="10" max="10" width="27.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="11.5546875" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="2" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E2" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="F2" t="b">
-        <v>0</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="C2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="F2" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J2" s="1" t="b">
+      <c r="J2" s="2" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F3" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="G3" t="s">
+      <c r="D3" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E3" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F3" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="J3" s="1" t="b">
+      <c r="J3" s="2" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="A4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D4" t="b">
-        <v>0</v>
-      </c>
-      <c r="E4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G4" t="s">
+      <c r="D4" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E4" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F4" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="J4" t="b">
+        <v>72</v>
+      </c>
+      <c r="J4" s="2" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="A5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G5" t="s">
+      <c r="D5" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E5" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="F5" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="H5" t="s">
+      <c r="H5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="I5" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="J5" t="b">
+      <c r="J5" s="2" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E6" t="b">
-        <v>1</v>
-      </c>
-      <c r="F6" t="b">
-        <v>0</v>
-      </c>
-      <c r="G6" t="s">
+      <c r="D6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="F6" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="H6" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="I6" s="2" t="s">
+      <c r="I6" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="J6" t="b">
+      <c r="J6" s="2" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="A7" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D7" t="b">
-        <v>1</v>
-      </c>
-      <c r="E7" t="b">
-        <v>1</v>
-      </c>
-      <c r="F7" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="G7" t="s">
+      <c r="D7" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E7" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="F7" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="G7" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="H7" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="I7" s="2" t="s">
+      <c r="I7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="J7" t="b">
+      <c r="J7" s="2" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C8" s="2" t="str">
+      <c r="C8" s="3" t="str">
         <f>"For BVP like in \textcite{"&amp;A7&amp;"}. For Augmentation like \textcite{"&amp;A6&amp;"}"</f>
         <v>For BVP like in \textcite{BanasikCrook2003SampleSelBias}. For Augmentation like \textcite{Banasik01032010}</v>
       </c>
-      <c r="D8" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="E8" t="b">
-        <v>1</v>
-      </c>
-      <c r="F8" t="b">
-        <v>0</v>
-      </c>
-      <c r="G8" t="s">
+      <c r="D8" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E8" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="F8" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="G8" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H8" s="2" t="s">
+      <c r="H8" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="I8" s="2" t="str">
+      <c r="I8" s="3" t="str">
         <f>"Also alike to \textcite{"&amp;A7&amp;"} and \textcite{"&amp;A6&amp;"}"</f>
         <v>Also alike to \textcite{BanasikCrook2003SampleSelBias} and \textcite{Banasik01032010}</v>
       </c>
-      <c r="J8" t="b">
+      <c r="J8" s="2" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+      <c r="A9" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C9" s="2" t="str">
+      <c r="C9" s="3" t="str">
         <f>"For Augmentation like \textcite{"&amp;A6&amp;"}, for extrapolation $\mathbb{P}(Y=g | X)$ similar in accepts and rejects"</f>
         <v>For Augmentation like \textcite{Banasik01032010}, for extrapolation $\mathbb{P}(Y=g | X)$ similar in accepts and rejects</v>
       </c>
-      <c r="D9" t="b">
-        <v>1</v>
-      </c>
-      <c r="E9" t="b">
-        <v>1</v>
-      </c>
-      <c r="F9" t="b">
-        <v>0</v>
-      </c>
-      <c r="G9" t="s">
+      <c r="D9" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E9" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="F9" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="G9" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H9" s="2" t="s">
+      <c r="H9" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="I9" s="1" t="str">
+      <c r="I9" s="2" t="str">
         <f>"Like \textcite{"&amp;A7&amp;"} and \textcite{"&amp;A6&amp;"}"</f>
         <v>Like \textcite{BanasikCrook2003SampleSelBias} and \textcite{Banasik01032010}</v>
       </c>
-      <c r="J9" t="b">
+      <c r="J9" s="2" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+      <c r="A10" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="D10" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="E10" t="b">
-        <v>0</v>
-      </c>
-      <c r="F10" t="b">
-        <v>0</v>
-      </c>
-      <c r="G10" t="s">
+      <c r="D10" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E10" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F10" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="G10" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H10" t="s">
+      <c r="H10" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I10" s="2" t="s">
+      <c r="I10" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="J10" t="b">
+      <c r="J10" s="2" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+      <c r="A11" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="3" t="s">
         <v>50</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="D11" t="b">
-        <v>1</v>
-      </c>
-      <c r="E11" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="F11" t="b">
-        <v>0</v>
-      </c>
-      <c r="G11" t="s">
+      <c r="D11" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E11" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="F11" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="G11" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H11" s="2" t="s">
+      <c r="H11" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="I11" s="2" t="s">
+      <c r="I11" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="J11" t="b">
+      <c r="J11" s="2" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="72" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="3" t="s">
         <v>57</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="D12" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="E12" t="b">
-        <v>1</v>
-      </c>
-      <c r="F12" t="b">
-        <v>0</v>
-      </c>
-      <c r="G12" t="s">
+      <c r="D12" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E12" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="F12" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="G12" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="H12" s="2" t="s">
+      <c r="H12" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="I12" s="2" t="s">
+      <c r="I12" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="J12" t="b">
+      <c r="J12" s="2" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="72" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+      <c r="A13" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D13" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E13" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="F13" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="J13" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D14" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E14" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="F14" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="J14" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="187.2" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D15" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E15" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F15" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="J15" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="201.6" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D16" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E16" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="F16" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="J16" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D17" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E17" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="F17" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="J17" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="72" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D18" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E18" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="F18" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="J18" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D19" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E19" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="F19" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="J19" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="187.2" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D20" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E20" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="F20" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="J20" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="345.6" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C13" t="s">
-        <v>61</v>
-      </c>
-      <c r="D13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E13" t="b">
-        <v>1</v>
-      </c>
-      <c r="F13" t="b">
-        <v>0</v>
-      </c>
-      <c r="G13" t="s">
-        <v>62</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="J13" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>66</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C14" t="s">
-        <v>68</v>
-      </c>
-      <c r="D14" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="E14" t="b">
-        <v>1</v>
-      </c>
-      <c r="F14" t="b">
-        <v>0</v>
-      </c>
-      <c r="G14" t="s">
-        <v>69</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="J14" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="187.2" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="D15" t="b">
-        <v>0</v>
-      </c>
-      <c r="E15" t="b">
-        <v>0</v>
-      </c>
-      <c r="F15" t="b">
-        <v>1</v>
-      </c>
-      <c r="G15" t="s">
+      <c r="B21" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D21" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E21" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F21" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G21" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H15" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="J15" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="201.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="D16" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="E16" t="b">
-        <v>1</v>
-      </c>
-      <c r="F16" t="b">
-        <v>0</v>
-      </c>
-      <c r="G16" t="s">
-        <v>78</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="J16" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="D17" t="b">
-        <v>1</v>
-      </c>
-      <c r="E17" t="b">
-        <v>1</v>
-      </c>
-      <c r="F17" t="b">
-        <v>0</v>
-      </c>
-      <c r="G17" t="s">
-        <v>85</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="J17" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" ht="72" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>88</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="D18" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="E18" t="b">
-        <v>1</v>
-      </c>
-      <c r="F18" t="b">
-        <v>0</v>
-      </c>
-      <c r="G18" t="s">
-        <v>91</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="J18" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>94</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="D19" t="b">
-        <v>0</v>
-      </c>
-      <c r="E19" t="b">
-        <v>1</v>
-      </c>
-      <c r="F19" t="b">
-        <v>0</v>
-      </c>
-      <c r="G19" t="s">
+      <c r="H21" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="J21" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="144" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="D22" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E22" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F22" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="G22" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H19" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J19" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="187.2" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>100</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="D20" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="E20" t="b">
-        <v>1</v>
-      </c>
-      <c r="F20" t="b">
-        <v>0</v>
-      </c>
-      <c r="G20" t="s">
+      <c r="H22" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="J22" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="273.60000000000002" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="D23" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E23" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="F23" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="G23" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H20" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="J20" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="345.6" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>106</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="D21" t="b">
-        <v>0</v>
-      </c>
-      <c r="E21" t="b">
-        <v>0</v>
-      </c>
-      <c r="F21" t="b">
-        <v>1</v>
-      </c>
-      <c r="G21" t="s">
-        <v>22</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="I21" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="J21" t="b">
-        <v>0</v>
-      </c>
+      <c r="H23" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="J23" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="187.2" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="D24" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E24" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="F24" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="J24" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K24" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/thesis/data/table_literature_review.xlsx
+++ b/thesis/data/table_literature_review.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mateo\Documents\Universidad\Master\Thesis\BEReBASL\thesis\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F721819-71F3-4893-B411-7FE9E5CA7FDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FC0B472-0BB9-4D01-B166-3EE1007AA954}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D47D74D5-B8DF-4140-AD42-DCD0A14E194D}"/>
   </bookViews>
@@ -405,19 +405,19 @@
     <t>Computational burden of training generative model, selecting the rate of generated samples, explainability</t>
   </si>
   <si>
-    <t>Confident Inlier Extrapolation (CI-EX): A semi-supervised framework that iteratively identifies non-outlier rejected samples per class using class-conditional Isolation Forest and assigns labels to the most confident candidates based on probabilities from a balanced classifier</t>
-  </si>
-  <si>
-    <t>Rejects are geomatric inliers relative to accepted samples and can be safely pseudo-labeled using classifier certainty. Iterative, controlled addition of confident inliers prevents catastrophic extrapolation drift. valuating RI solely on accepted test sets (via standard AUC) is fundamentally biased, requiring population/debiased metrics like Kickout and Area Under the Kickout (AUK)</t>
-  </si>
-  <si>
     <t>Emp. and sim.</t>
   </si>
   <si>
-    <t>Moderately / Trade-off dependent</t>
-  </si>
-  <si>
-    <t>Managing the explicit trade-off between maximizing population debiasing (AUK) and maintaining accepted-set accuracy (AUC), alongside the computational overhead of multi-step iterative retraining</t>
+    <t>Managing the explicit trade-off between maximizing population debiasing (AUK) and maintaining accepted-set accuracy (AUC), alongside the computational overhead of multi-step iterative retraining, handling same features in rejects and accepts</t>
+  </si>
+  <si>
+    <t>Moderately, Trade-off dependent measured on accepts' AUC and Kickout\footnote{A RI-directed measure}</t>
+  </si>
+  <si>
+    <t>Confident Inlier Extrapolation (CI-EX): A semi-supervised framework that iteratively identifies non-outlier rejected samples per class using class-conditional Isolation Forest and assigns labels to at most the $c \in \mathbb{N}$ most confident candidates based on probabilities from a balanced\footnote{In the sense that observations are weighted to account for class imbalance} classifier</t>
+  </si>
+  <si>
+    <t>IFO inliers with high condifence is enough to avoid inferring too many wrong labels. Fully unbiasing is not necessarily sensible. IFO is adequate for outlier detection. Implicitly: likely MAR (or close to)\footnote{Otherwise using a scoring model that is calculated without extra assumptions and without estimating AR would be senseless}</t>
   </si>
 </sst>
 </file>
@@ -1562,31 +1562,31 @@
         <v>112</v>
       </c>
       <c r="B24" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="D24" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E24" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="F24" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="G24" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="H24" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="I24" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="D24" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E24" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="F24" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>125</v>
-      </c>
       <c r="J24" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K24" s="1"/>
     </row>

--- a/thesis/data/table_literature_review.xlsx
+++ b/thesis/data/table_literature_review.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mateo\Documents\Universidad\Master\Thesis\BEReBASL\thesis\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FC0B472-0BB9-4D01-B166-3EE1007AA954}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C77D21F0-40E1-4138-84B7-2273575A01C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D47D74D5-B8DF-4140-AD42-DCD0A14E194D}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="128">
   <si>
     <t>Reference</t>
   </si>
@@ -59,9 +59,6 @@
     <t>HandHanley1993CanRIWork</t>
   </si>
   <si>
-    <t>Knowledge and existence of causal non-cyclic relationships between features</t>
-  </si>
-  <si>
     <t>Moderately</t>
   </si>
   <si>
@@ -95,9 +92,6 @@
     <t>Does RI work?</t>
   </si>
   <si>
-    <t>Only with labeled rejects' smaple</t>
-  </si>
-  <si>
     <t>Augmentation inadequate for RI</t>
   </si>
   <si>
@@ -116,9 +110,6 @@
     <t>Assump. explicit?</t>
   </si>
   <si>
-    <t>Infers Rejects' label for eval?</t>
-  </si>
-  <si>
     <t>Independence condition\footnote{The condition comes from the cited paper \cite{BuckerKramer2011} in the proof} illogical in dynamic context, numerical problems</t>
   </si>
   <si>
@@ -137,9 +128,6 @@
     <t>Moderately if MNAR and conservative FI</t>
   </si>
   <si>
-    <t>Errors in modelled equations are correlated, knowledge of relevant variables</t>
-  </si>
-  <si>
     <t>Bivariate Probit for PD and AR equations (BVP)</t>
   </si>
   <si>
@@ -209,9 +197,6 @@
     <t>Feelders2000RIMixtureModels</t>
   </si>
   <si>
-    <t>MAR</t>
-  </si>
-  <si>
     <t>EM algorithm, for rejects explicit expectation over the two classes weighted by the posterior</t>
   </si>
   <si>
@@ -248,9 +233,6 @@
     <t>Emp. with simulated cutoff</t>
   </si>
   <si>
-    <t>Yes, measured on artificial reject/accept region of past credits</t>
-  </si>
-  <si>
     <t>Data needed scales strongly with range of scores, unclear how the data is MNAR</t>
   </si>
   <si>
@@ -296,9 +278,6 @@
     <t>Sim. and Emp.</t>
   </si>
   <si>
-    <t>Yes for evaluation, estimation also under specific conditions</t>
-  </si>
-  <si>
     <t>BASL: sensitivity to class imbalance, understanding when it is worthwhile using it</t>
   </si>
   <si>
@@ -312,9 +291,6 @@
   </si>
   <si>
     <t>Sim. And Emp.</t>
-  </si>
-  <si>
-    <t>Yes in sim., in emp. also with artificial rejects\footnote{meaning: rejects among the accepted clients in the samples}</t>
   </si>
   <si>
     <t>Linearity constraint, high dimensional feature space, handling large amounts of data</t>
@@ -333,12 +309,6 @@
     <t>Computational costs scale with reject rate, ensuring non-overfitted well calibrated classifier</t>
   </si>
   <si>
-    <t>Yes, on holdout accepts</t>
-  </si>
-  <si>
-    <t>Moderately based on accepts only eval.</t>
-  </si>
-  <si>
     <t>ShenEtAl2020ThreeStageRI</t>
   </si>
   <si>
@@ -348,9 +318,6 @@
     <t>STL will produce features better aligned for credit scoring using \textit{any downstream algorithm} as it does not assume equal distributions of accepts and rejects. MD serves as proxy to prevent negative transferin STL by including only rejects features alike to the accepts, which allows to induce they assume the data is not MNAR. MD is suitable for a mix of contiguous, binary and categorical data</t>
   </si>
   <si>
-    <t>Yes, on holdout accepts\footnote{They did however not check if the improvement comes from higher feature representation learning or from RI}</t>
-  </si>
-  <si>
     <t>Extremeley High computational costs due to 3WD, explainability and credibility</t>
   </si>
   <si>
@@ -363,9 +330,6 @@
     <t>A Kernel-free Fuzzy Quadratic Surface SVM (FQSSVM) approach consisting of: initial FQSSVM-separation to compute eucl. distance metrics to boundary; outlier detection using local neighborhood affinity to eliminate default outliers with rejects seen as bads from here on; a fuzzy weighting scheme based on class centers, local hesitation, and proximity to the boundary, where potentially good rejects recieve small missclasification penalization weights; and convex FQSSVM optimization on both accepted and weighted, temporarily labeled rejected samples</t>
   </si>
   <si>
-    <t>Yes, with rejects' labels were (partially) inferred</t>
-  </si>
-  <si>
     <t>MAR DGP, all rejects as bad appropiate for initial separation. Accepted default borrowers with excellent attributes are ``outliers" (accidental defaults) whose elimination improves classification accuracy\footnote{This assumption implies a series of assumptions alike to the model presented in \ref{sec-measure-theoretic-desc-ri-problem}}. Rejects positioned near the initial separating boundary represent potential good borrowers, meaning the separation boundary is assumed to be already near optimal. Quadratic surface a good approximator of ``any" separation boundary\footnote{Which cannot be, their argument on taylor approximation is taken to be too general}</t>
   </si>
   <si>
@@ -381,9 +345,6 @@
     <t>ribeiro2025balancingperformancerejectinclusion</t>
   </si>
   <si>
-    <t>Moderately based on accepts only eval</t>
-  </si>
-  <si>
     <t>Estimate Isolation Forest (IFO) on rejects to label them: outliers as goods, inliers as bad where this classification happens through heuristic setting of Contamination Rate (CR). Then LightGBM on rejects and accepts where missing values of rejects' features are set to 0 and all features are 0-1 normalized</t>
   </si>
   <si>
@@ -399,25 +360,71 @@
     <t>Likely MNAR\footnote{As they model explicitly the Accept/Reject decision, not explicitly formulated}. Same features among accepts and rejects. Virtual label mechanism for rejects does not bias the generative process and does not need weighting these observations. The same latent feature representations for rejects works for modeling GB and AR equations. That specific AR modeling alleviates the bias on GB.</t>
   </si>
   <si>
-    <t>On holdout accept: yes for rebalancing and moderately prediction\footnote{The greatest gain in prediction comes from the rebalancing, the MLT part was not benchmarked to other methods considering auxiliary tasks like Heckman's model}</t>
-  </si>
-  <si>
     <t>Computational burden of training generative model, selecting the rate of generated samples, explainability</t>
   </si>
   <si>
-    <t>Emp. and sim.</t>
-  </si>
-  <si>
     <t>Managing the explicit trade-off between maximizing population debiasing (AUK) and maintaining accepted-set accuracy (AUC), alongside the computational overhead of multi-step iterative retraining, handling same features in rejects and accepts</t>
   </si>
   <si>
-    <t>Moderately, Trade-off dependent measured on accepts' AUC and Kickout\footnote{A RI-directed measure}</t>
-  </si>
-  <si>
     <t>Confident Inlier Extrapolation (CI-EX): A semi-supervised framework that iteratively identifies non-outlier rejected samples per class using class-conditional Isolation Forest and assigns labels to at most the $c \in \mathbb{N}$ most confident candidates based on probabilities from a balanced\footnote{In the sense that observations are weighted to account for class imbalance} classifier</t>
   </si>
   <si>
     <t>IFO inliers with high condifence is enough to avoid inferring too many wrong labels. Fully unbiasing is not necessarily sensible. IFO is adequate for outlier detection. Implicitly: likely MAR (or close to)\footnote{Otherwise using a scoring model that is calculated without extra assumptions and without estimating AR would be senseless}</t>
+  </si>
+  <si>
+    <t>Errors in modelled equations are correlated, knowledge of relevant variables, MNAR</t>
+  </si>
+  <si>
+    <t>MAR, parametric classifier</t>
+  </si>
+  <si>
+    <t>Only with labeled rejects' sample</t>
+  </si>
+  <si>
+    <t>Knowledge and existence of causal non-cyclic relationships between features. Implicitly MAR</t>
+  </si>
+  <si>
+    <t>$\mathbf{A} + \mathbf{R}_e$</t>
+  </si>
+  <si>
+    <t>$\mathbf{A}$</t>
+  </si>
+  <si>
+    <t>$\mathbf{A} + \mathbf{R}$</t>
+  </si>
+  <si>
+    <t>Test Pool</t>
+  </si>
+  <si>
+    <t>$\mathbf{A}$, $\mathbf{A}$ under new policy</t>
+  </si>
+  <si>
+    <t>Sim: $\mathbf{A} + \mathbf{R}$
+Emp: $\mathbf{AR}_s$</t>
+  </si>
+  <si>
+    <t>Yes for eval., estimation also under specific conditions</t>
+  </si>
+  <si>
+    <t>$\mathbf{A}$, $\mathbf{A} + \mathbf{R}_e$</t>
+  </si>
+  <si>
+    <t>Yes, on $\mathbf{A}$</t>
+  </si>
+  <si>
+    <t>$\emptyset$</t>
+  </si>
+  <si>
+    <t>$\mathbf{AR}_s$</t>
+  </si>
+  <si>
+    <t>Yes\footnote{They did however not check if the improvement comes from higher feature representation learning or from RI}</t>
+  </si>
+  <si>
+    <t>Yes for rebalancing and moderately prediction\footnote{The greatest gain in prediction comes from the rebalancing, the MLT part was not benchmarked to other methods considering auxiliary tasks like Heckman's model}</t>
+  </si>
+  <si>
+    <t>Moderately, Trade-off dependent between AUC and Kickout\footnote{A RI-directed measure}</t>
   </si>
 </sst>
 </file>
@@ -461,13 +468,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -802,55 +812,53 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8852FF5C-5175-44DA-A620-18833DBB2C7A}">
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="38.33203125" style="2" customWidth="1"/>
-    <col min="2" max="3" width="28.21875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="21.88671875" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.6640625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="28.6640625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="24.88671875" style="2" customWidth="1"/>
-    <col min="8" max="8" width="27.44140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="27.44140625" style="2" customWidth="1"/>
-    <col min="10" max="10" width="27.88671875" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="11.5546875" style="2"/>
+    <col min="1" max="1" width="38.33203125" customWidth="1"/>
+    <col min="2" max="3" width="28.21875" customWidth="1"/>
+    <col min="4" max="4" width="21.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.6640625" customWidth="1"/>
+    <col min="6" max="7" width="24.88671875" customWidth="1"/>
+    <col min="8" max="8" width="27.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="27.44140625" customWidth="1"/>
+    <col min="10" max="10" width="27.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G1" s="2" t="s">
+      <c r="D1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1" t="s">
+        <v>117</v>
+      </c>
+      <c r="H1" t="s">
         <v>16</v>
       </c>
-      <c r="H1" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" t="s">
         <v>3</v>
       </c>
-      <c r="J1" s="2" t="s">
-        <v>21</v>
+      <c r="J1" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+      <c r="A2" t="s">
         <v>5</v>
       </c>
       <c r="B2" s="3" t="s">
@@ -859,736 +867,739 @@
       <c r="C2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E2" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="F2" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>27</v>
+      <c r="D2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E2" t="b">
+        <v>1</v>
+      </c>
+      <c r="F2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G2" t="s">
+        <v>123</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>18</v>
+        <v>112</v>
       </c>
       <c r="I2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J2" s="2" t="b">
+      <c r="J2" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="D3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" t="s">
+        <v>115</v>
+      </c>
+      <c r="H3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E3" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F3" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H3" s="2" t="s">
+      <c r="B4" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G4" t="s">
+        <v>114</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="J4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="H5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
         <v>7</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="B6" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E6" t="b">
+        <v>1</v>
+      </c>
+      <c r="F6" t="s">
         <v>20</v>
       </c>
-      <c r="J3" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D4" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="E4" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F4" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="J4" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D5" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E5" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="F5" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="G5" s="2" t="s">
+      <c r="G6" t="s">
+        <v>115</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="D7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E7" t="b">
+        <v>1</v>
+      </c>
+      <c r="F7" t="s">
+        <v>27</v>
+      </c>
+      <c r="G7" t="s">
+        <v>116</v>
+      </c>
+      <c r="H7" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="H5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="J5" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C6" s="3" t="s">
+      <c r="I7" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="J7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
         <v>35</v>
       </c>
-      <c r="D6" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E6" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="F6" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="J6" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D7" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E7" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="F7" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="G7" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="H7" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="J7" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C8" s="3" t="str">
+      <c r="C8" s="2" t="str">
         <f>"For BVP like in \textcite{"&amp;A7&amp;"}. For Augmentation like \textcite{"&amp;A6&amp;"}"</f>
         <v>For BVP like in \textcite{BanasikCrook2003SampleSelBias}. For Augmentation like \textcite{Banasik01032010}</v>
       </c>
-      <c r="D8" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E8" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="F8" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>22</v>
+      <c r="D8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E8" t="b">
+        <v>1</v>
+      </c>
+      <c r="F8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G8" t="s">
+        <v>116</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I8" s="3" t="str">
         <f>"Also alike to \textcite{"&amp;A7&amp;"} and \textcite{"&amp;A6&amp;"}"</f>
         <v>Also alike to \textcite{BanasikCrook2003SampleSelBias} and \textcite{Banasik01032010}</v>
       </c>
-      <c r="J8" s="2" t="b">
+      <c r="J8" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
-        <v>40</v>
+      <c r="A9" t="s">
+        <v>36</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C9" s="3" t="str">
         <f>"For Augmentation like \textcite{"&amp;A6&amp;"}, for extrapolation $\mathbb{P}(Y=g | X)$ similar in accepts and rejects"</f>
         <v>For Augmentation like \textcite{Banasik01032010}, for extrapolation $\mathbb{P}(Y=g | X)$ similar in accepts and rejects</v>
       </c>
-      <c r="D9" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E9" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="F9" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>22</v>
+      <c r="D9" t="b">
+        <v>1</v>
+      </c>
+      <c r="E9" t="b">
+        <v>1</v>
+      </c>
+      <c r="F9" t="s">
+        <v>20</v>
+      </c>
+      <c r="G9" t="s">
+        <v>116</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I9" s="2" t="str">
+        <v>14</v>
+      </c>
+      <c r="I9" t="str">
         <f>"Like \textcite{"&amp;A7&amp;"} and \textcite{"&amp;A6&amp;"}"</f>
         <v>Like \textcite{BanasikCrook2003SampleSelBias} and \textcite{Banasik01032010}</v>
       </c>
-      <c r="J9" s="2" t="b">
+      <c r="J9" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
+      <c r="A10" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" t="s">
+        <v>40</v>
+      </c>
+      <c r="C10" t="s">
+        <v>41</v>
+      </c>
+      <c r="D10" t="b">
+        <v>1</v>
+      </c>
+      <c r="E10" t="b">
+        <v>0</v>
+      </c>
+      <c r="F10" t="s">
+        <v>20</v>
+      </c>
+      <c r="G10" t="s">
+        <v>115</v>
+      </c>
+      <c r="H10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="J10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
         <v>43</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D10" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E10" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F10" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I10" s="3" t="s">
+      <c r="B11" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="J10" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B11" s="3" t="s">
+      <c r="C11" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D11" t="b">
+        <v>1</v>
+      </c>
+      <c r="E11" t="b">
+        <v>1</v>
+      </c>
+      <c r="F11" t="s">
+        <v>20</v>
+      </c>
+      <c r="G11" t="s">
+        <v>115</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I11" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="J11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="72" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>51</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="D12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E12" t="b">
+        <v>1</v>
+      </c>
+      <c r="F12" t="s">
         <v>53</v>
       </c>
-      <c r="D11" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E11" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="F11" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I11" s="3" t="s">
+      <c r="G12" t="s">
+        <v>116</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="I12" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="J11" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="72" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B12" s="3" t="s">
+      <c r="J12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="72" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>93</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E13" t="b">
+        <v>1</v>
+      </c>
+      <c r="F13" t="s">
+        <v>27</v>
+      </c>
+      <c r="G13" t="s">
+        <v>123</v>
+      </c>
+      <c r="H13" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="D12" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E12" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="F12" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="G12" s="2" t="s">
+      <c r="I13" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="H12" s="3" t="s">
+      <c r="J13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
         <v>60</v>
       </c>
-      <c r="I12" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="J12" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="72" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
+      <c r="B14" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C14" t="s">
+        <v>62</v>
+      </c>
+      <c r="D14" t="b">
+        <v>0</v>
+      </c>
+      <c r="E14" t="b">
+        <v>1</v>
+      </c>
+      <c r="F14" t="s">
+        <v>63</v>
+      </c>
+      <c r="G14" t="s">
+        <v>124</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="J14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="187.2" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>65</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D15" t="b">
+        <v>0</v>
+      </c>
+      <c r="E15" t="b">
+        <v>0</v>
+      </c>
+      <c r="F15" t="s">
+        <v>20</v>
+      </c>
+      <c r="G15" t="s">
+        <v>121</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="J15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="201.6" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>70</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E16" t="b">
+        <v>1</v>
+      </c>
+      <c r="F16" t="s">
+        <v>71</v>
+      </c>
+      <c r="G16" t="s">
+        <v>118</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="J16" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>74</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D17" t="b">
+        <v>1</v>
+      </c>
+      <c r="E17" t="b">
+        <v>1</v>
+      </c>
+      <c r="F17" t="s">
+        <v>78</v>
+      </c>
+      <c r="G17" t="s">
+        <v>116</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="J17" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="72" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>80</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D18" t="b">
+        <v>1</v>
+      </c>
+      <c r="E18" t="b">
+        <v>1</v>
+      </c>
+      <c r="F18" t="s">
+        <v>83</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="J18" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>85</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D19" t="b">
+        <v>0</v>
+      </c>
+      <c r="E19" t="b">
+        <v>1</v>
+      </c>
+      <c r="F19" t="s">
+        <v>20</v>
+      </c>
+      <c r="G19" t="s">
+        <v>115</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="J19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="187.2" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>89</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D20" t="b">
+        <v>0</v>
+      </c>
+      <c r="E20" t="b">
+        <v>1</v>
+      </c>
+      <c r="F20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G20" t="s">
+        <v>115</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="J20" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="345.6" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>94</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D21" t="b">
+        <v>0</v>
+      </c>
+      <c r="E21" t="b">
+        <v>0</v>
+      </c>
+      <c r="F21" t="s">
+        <v>20</v>
+      </c>
+      <c r="G21" t="s">
+        <v>114</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I21" t="s">
+        <v>97</v>
+      </c>
+      <c r="J21" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="144" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>98</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="D22" t="b">
+        <v>0</v>
+      </c>
+      <c r="E22" t="b">
+        <v>0</v>
+      </c>
+      <c r="F22" t="s">
+        <v>20</v>
+      </c>
+      <c r="G22" t="s">
+        <v>115</v>
+      </c>
+      <c r="H22" t="s">
+        <v>6</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="J22" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="273.60000000000002" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>99</v>
+      </c>
+      <c r="B23" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D13" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E13" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="F13" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="J13" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D14" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="E14" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="F14" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="J14" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="187.2" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D15" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="E15" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F15" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="J15" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="201.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="D16" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E16" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="F16" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="J16" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="D17" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E17" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="F17" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="J17" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" ht="72" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D18" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E18" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="F18" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="J18" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A19" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="D19" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="E19" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="F19" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="J19" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" ht="187.2" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="B20" s="3" t="s">
+      <c r="C23" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="D23" t="b">
+        <v>0</v>
+      </c>
+      <c r="E23" t="b">
+        <v>1</v>
+      </c>
+      <c r="F23" t="s">
+        <v>20</v>
+      </c>
+      <c r="G23" t="s">
+        <v>115</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="J23" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="187.2" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
         <v>100</v>
       </c>
-      <c r="C20" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="D20" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="E20" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="F20" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="J20" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" ht="345.6" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="C21" s="3" t="s">
+      <c r="B24" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="D21" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="E21" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F21" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H21" s="3" t="s">
+      <c r="C24" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="D24" t="b">
+        <v>1</v>
+      </c>
+      <c r="E24" t="b">
+        <v>1</v>
+      </c>
+      <c r="F24" t="s">
+        <v>20</v>
+      </c>
+      <c r="G24" t="s">
+        <v>124</v>
+      </c>
+      <c r="H24" t="s">
+        <v>127</v>
+      </c>
+      <c r="I24" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="I21" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="J21" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" ht="144" x14ac:dyDescent="0.3">
-      <c r="A22" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="D22" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="E22" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F22" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="J22" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" ht="273.60000000000002" x14ac:dyDescent="0.3">
-      <c r="A23" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="D23" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="E23" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="F23" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="J23" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" ht="187.2" x14ac:dyDescent="0.3">
-      <c r="A24" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="D24" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E24" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="F24" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="J24" s="2" t="b">
+      <c r="J24" t="b">
         <v>0</v>
       </c>
       <c r="K24" s="1"/>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="F25" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/thesis/data/table_literature_review.xlsx
+++ b/thesis/data/table_literature_review.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mateo\Documents\Universidad\Master\Thesis\BEReBASL\thesis\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C77D21F0-40E1-4138-84B7-2273575A01C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6631AF3F-B4B8-4650-AE51-1C1054104685}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D47D74D5-B8DF-4140-AD42-DCD0A14E194D}"/>
   </bookViews>
@@ -272,9 +272,6 @@
     <t>Bayesian Evaluation: Use random conditional bernoulli based extrapolation on evaluation set iteratively to get bayesian metric. For inference: iteratively partially extrapolate to generate high confidence rejects' labels to generate larger complete data for training scorecard</t>
   </si>
   <si>
-    <t>MAR or MNAR data, partial debiasing is more useful than extrapolating all rejects, rejects contain higher bad rates, posterior estimate can be calibrated</t>
-  </si>
-  <si>
     <t>Sim. and Emp.</t>
   </si>
   <si>
@@ -425,6 +422,9 @@
   </si>
   <si>
     <t>Moderately, Trade-off dependent between AUC and Kickout\footnote{A RI-directed measure}</t>
+  </si>
+  <si>
+    <t>MAR or MNAR data, partial debiasing is more useful than extrapolating all rejects, rejects contain higher bad rates, posterior estimate can be calibrated\footnote{See that this is specially important for the Bayesian Evaluation method, which uses the posterior to repeteadly calculate a metric until convergence}</t>
   </si>
 </sst>
 </file>
@@ -845,7 +845,7 @@
         <v>15</v>
       </c>
       <c r="G1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H1" t="s">
         <v>16</v>
@@ -877,10 +877,10 @@
         <v>24</v>
       </c>
       <c r="G2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I2" s="3" t="s">
         <v>4</v>
@@ -897,7 +897,7 @@
         <v>38</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D3" t="b">
         <v>1</v>
@@ -909,7 +909,7 @@
         <v>20</v>
       </c>
       <c r="G3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H3" t="s">
         <v>6</v>
@@ -941,7 +941,7 @@
         <v>20</v>
       </c>
       <c r="G4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>13</v>
@@ -973,7 +973,7 @@
         <v>25</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H5" t="s">
         <v>13</v>
@@ -1005,7 +1005,7 @@
         <v>20</v>
       </c>
       <c r="G6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>34</v>
@@ -1025,7 +1025,7 @@
         <v>29</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D7" t="b">
         <v>1</v>
@@ -1037,7 +1037,7 @@
         <v>27</v>
       </c>
       <c r="G7" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>28</v>
@@ -1070,7 +1070,7 @@
         <v>20</v>
       </c>
       <c r="G8" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>14</v>
@@ -1104,7 +1104,7 @@
         <v>20</v>
       </c>
       <c r="G9" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>14</v>
@@ -1137,7 +1137,7 @@
         <v>20</v>
       </c>
       <c r="G10" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H10" t="s">
         <v>13</v>
@@ -1169,7 +1169,7 @@
         <v>20</v>
       </c>
       <c r="G11" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>13</v>
@@ -1189,7 +1189,7 @@
         <v>52</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D12" t="b">
         <v>1</v>
@@ -1201,7 +1201,7 @@
         <v>53</v>
       </c>
       <c r="G12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>55</v>
@@ -1215,7 +1215,7 @@
     </row>
     <row r="13" spans="1:10" ht="72" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>59</v>
@@ -1233,7 +1233,7 @@
         <v>27</v>
       </c>
       <c r="G13" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>57</v>
@@ -1265,7 +1265,7 @@
         <v>63</v>
       </c>
       <c r="G14" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>13</v>
@@ -1297,10 +1297,10 @@
         <v>20</v>
       </c>
       <c r="G15" t="s">
+        <v>120</v>
+      </c>
+      <c r="H15" s="3" t="s">
         <v>121</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>122</v>
       </c>
       <c r="I15" s="3" t="s">
         <v>69</v>
@@ -1329,7 +1329,7 @@
         <v>71</v>
       </c>
       <c r="G16" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>13</v>
@@ -1341,7 +1341,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>74</v>
       </c>
@@ -1349,25 +1349,25 @@
         <v>76</v>
       </c>
       <c r="C17" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="D17" t="b">
+        <v>1</v>
+      </c>
+      <c r="E17" t="b">
+        <v>1</v>
+      </c>
+      <c r="F17" t="s">
         <v>77</v>
       </c>
-      <c r="D17" t="b">
-        <v>1</v>
-      </c>
-      <c r="E17" t="b">
-        <v>1</v>
-      </c>
-      <c r="F17" t="s">
+      <c r="G17" t="s">
+        <v>115</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="I17" s="3" t="s">
         <v>78</v>
-      </c>
-      <c r="G17" t="s">
-        <v>116</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>79</v>
       </c>
       <c r="J17" t="b">
         <v>0</v>
@@ -1375,31 +1375,31 @@
     </row>
     <row r="18" spans="1:11" ht="72" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
+        <v>79</v>
+      </c>
+      <c r="B18" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="C18" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="D18" t="b">
+        <v>1</v>
+      </c>
+      <c r="E18" t="b">
+        <v>1</v>
+      </c>
+      <c r="F18" t="s">
         <v>82</v>
       </c>
-      <c r="D18" t="b">
-        <v>1</v>
-      </c>
-      <c r="E18" t="b">
-        <v>1</v>
-      </c>
-      <c r="F18" t="s">
-        <v>83</v>
-      </c>
       <c r="G18" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J18" t="b">
         <v>0</v>
@@ -1407,13 +1407,13 @@
     </row>
     <row r="19" spans="1:11" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
+        <v>84</v>
+      </c>
+      <c r="B19" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="C19" s="3" t="s">
         <v>86</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>87</v>
       </c>
       <c r="D19" t="b">
         <v>0</v>
@@ -1425,13 +1425,13 @@
         <v>20</v>
       </c>
       <c r="G19" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J19" t="b">
         <v>0</v>
@@ -1439,13 +1439,13 @@
     </row>
     <row r="20" spans="1:11" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
+        <v>88</v>
+      </c>
+      <c r="B20" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="C20" s="3" t="s">
         <v>90</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="D20" t="b">
         <v>0</v>
@@ -1457,13 +1457,13 @@
         <v>20</v>
       </c>
       <c r="G20" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J20" t="b">
         <v>0</v>
@@ -1471,13 +1471,13 @@
     </row>
     <row r="21" spans="1:11" ht="345.6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
+        <v>93</v>
+      </c>
+      <c r="B21" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="C21" s="3" t="s">
         <v>95</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>96</v>
       </c>
       <c r="D21" t="b">
         <v>0</v>
@@ -1489,13 +1489,13 @@
         <v>20</v>
       </c>
       <c r="G21" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I21" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J21" t="b">
         <v>0</v>
@@ -1503,13 +1503,13 @@
     </row>
     <row r="22" spans="1:11" ht="144" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D22" t="b">
         <v>0</v>
@@ -1521,13 +1521,13 @@
         <v>20</v>
       </c>
       <c r="G22" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H22" t="s">
         <v>6</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="J22" t="b">
         <v>0</v>
@@ -1535,13 +1535,13 @@
     </row>
     <row r="23" spans="1:11" ht="273.60000000000002" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B23" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>104</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>105</v>
       </c>
       <c r="D23" t="b">
         <v>0</v>
@@ -1553,13 +1553,13 @@
         <v>20</v>
       </c>
       <c r="G23" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="J23" t="b">
         <v>0</v>
@@ -1567,13 +1567,13 @@
     </row>
     <row r="24" spans="1:11" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B24" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>108</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>109</v>
       </c>
       <c r="D24" t="b">
         <v>1</v>
@@ -1585,13 +1585,13 @@
         <v>20</v>
       </c>
       <c r="G24" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H24" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="J24" t="b">
         <v>0</v>
